--- a/교육자료/양식/_담당자용/04_업무분배시트.xlsx
+++ b/교육자료/양식/_담당자용/04_업무분배시트.xlsx
@@ -13,7 +13,6 @@
     <sheet name="직원2" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="직원3" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="직원4" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="직원5" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -596,7 +595,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>「직원1」~「직원5」 시트에 이름·브랜드·키워드·계정을 채웁니다.</t>
+          <t>「직원1」~「직원4」 시트에 이름·브랜드·키워드·계정을 채웁니다.</t>
         </is>
       </c>
     </row>
@@ -627,7 +626,7 @@
     <row r="9">
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>※ 인원이 5명이 아니면 _build_assign_xlsx.py 의 PEOPLE 값을 바꿔서 다시 실행하세요.</t>
+          <t>※ 인원이 4명이 아니면 _build_assign_xlsx.py 의 PEOPLE 값을 바꿔서 다시 실행하세요.</t>
         </is>
       </c>
     </row>
@@ -667,7 +666,7 @@
     <row r="2">
       <c r="A2" s="4" t="inlineStr">
         <is>
-          <t>※ 담당자 칸을 채우면 됩니다. 1인 1~2개를 권합니다. 통검표 주소를 눌러 바로 열 수 있습니다.</t>
+          <t>※ 이번은 4명 / 1인 1브랜드 — 퍼스트디자인·하오디자인·하오스튜디오·윈차이나. 하오팩토리·레드트랜스는 미배정(설명만). 통검표 주소를 눌러 바로 열 수 있습니다.</t>
         </is>
       </c>
     </row>
@@ -4755,920 +4754,4 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E61"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>업무 배정서</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>미얀마 마케터 교육 · 2026.09.16(수) ~ 09.24(목) 8회차 · 이 종이를 옆에 두고 봅니다</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>1. 나</t>
-        </is>
-      </c>
-      <c r="B4" s="12" t="n"/>
-      <c r="C4" s="12" t="n"/>
-      <c r="D4" s="12" t="n"/>
-      <c r="E4" s="12" t="n"/>
-    </row>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="13" t="inlineStr">
-        <is>
-          <t>이름</t>
-        </is>
-      </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>교육 시작일</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr">
-        <is>
-          <t>2026-09-16 (수)</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>담당자(한국)</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr">
-        <is>
-          <t>이름 / 연락 방법</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-    </row>
-    <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>2. 내 브랜드</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="inlineStr"/>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>사이트</t>
-        </is>
-      </c>
-      <c r="D10" s="5" t="inlineStr">
-        <is>
-          <t>하는 일</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>메모</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>첫 번째</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-    </row>
-    <row r="12" ht="34" customHeight="1">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>두 번째</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-    </row>
-    <row r="13" ht="44" customHeight="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>원고 2가지</t>
-        </is>
-      </c>
-      <c r="B13" s="15" t="inlineStr">
-        <is>
-          <t>홍보성(○○제작·비용 — 업체 찾는 사람) / 정보성(○○방법·필요서류 — 절차 모르는 사람). 브랜드와 관계없이 두 방향이 다 나온다. 쓰기 전에 어느 쪽인지 먼저 정할 것</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-    </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>★ 내 통검표 주소</t>
-        </is>
-      </c>
-      <c r="B14" s="15" t="inlineStr">
-        <is>
-          <t>브랜드별 「OO 통합시트」 주소. 매일 여는 곳입니다 (계정시트 「통검표주소」 시트 참고)</t>
-        </is>
-      </c>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-    </row>
-    <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>우리가 안 하는 일</t>
-        </is>
-      </c>
-      <c r="B15" s="15" t="inlineStr">
-        <is>
-          <t>홈페이지를 읽고 직접 적기 — 없는 서비스를 광고하는 글을 막아줍니다</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-    </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>쓰면 안 되는 표현</t>
-        </is>
-      </c>
-      <c r="B16" s="15" t="inlineStr">
-        <is>
-          <t>최저가 · 1위 · 100% · 무조건 · 최고 / 확인 안 된 가격·기간 / 경쟁사 이름</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-    </row>
-    <row r="17" ht="52" customHeight="1">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>★★ 사진 규칙</t>
-        </is>
-      </c>
-      <c r="B17" s="16" t="inlineStr">
-        <is>
-          <t>구글·네이버에서 검색해서 나온 사진은 절대 금지. ① 회사 사진 폴더(구글 드라이브)  ② 클립아트코리아  ③ 프리픽(목업 전용)  ④ GPT 생성 — 이것만. 사진은 카드뉴스에 넣는 것이므로 카드뉴스와 한 번에 작업</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="n"/>
-      <c r="D17" s="17" t="n"/>
-      <c r="E17" s="17" t="n"/>
-    </row>
-    <row r="19" ht="24" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
-        <is>
-          <t>3. 내 키워드</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-    </row>
-    <row r="20" ht="24" customHeight="1">
-      <c r="A20" s="5" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>키워드</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="inlineStr">
-        <is>
-          <t>브랜드</t>
-        </is>
-      </c>
-      <c r="D20" s="5" t="inlineStr">
-        <is>
-          <t>상태</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
-        <is>
-          <t>발행일 / 링크</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="n"/>
-      <c r="E21" s="8" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="n"/>
-      <c r="E23" s="8" t="n"/>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="n"/>
-      <c r="E24" s="8" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="n"/>
-      <c r="E25" s="8" t="n"/>
-    </row>
-    <row r="26" ht="40" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>내가 쓰면 안 되는 키워드</t>
-        </is>
-      </c>
-      <c r="B26" s="16" t="inlineStr">
-        <is>
-          <t>다른 사람에게 배정된 키워드를 적어둡니다 — 겹치면 우리끼리 자리를 뺏습니다</t>
-        </is>
-      </c>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="17" t="n"/>
-    </row>
-    <row r="28" ht="24" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>4. 내 계정</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>네이버 아이디</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="14" t="n"/>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="14" t="n"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>내 블로그 주소</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="14" t="n"/>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="14" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>★ 내 한국 PC 애니데스크 주소</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>지금은 이걸로 네이버 작업 — 사람마다 정해져 있음</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n"/>
-      <c r="D31" s="14" t="n"/>
-      <c r="E31" s="14" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>애니데스크 접속 비밀번호</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>담당자에게 받기 (여기 적지 말 것)</t>
-        </is>
-      </c>
-      <c r="C32" s="14" t="n"/>
-      <c r="D32" s="14" t="n"/>
-      <c r="E32" s="14" t="n"/>
-    </row>
-    <row r="33" ht="22" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>고정 IP 아이디</t>
-        </is>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>담당자가 다시 쓰라고 할 때만</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="n"/>
-      <c r="D33" s="14" t="n"/>
-      <c r="E33" s="14" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>내 IP 주소</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>그때 이 숫자와 같은지 확인</t>
-        </is>
-      </c>
-      <c r="C34" s="14" t="n"/>
-      <c r="D34" s="14" t="n"/>
-      <c r="E34" s="14" t="n"/>
-    </row>
-    <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>유료 이미지 사이트</t>
-        </is>
-      </c>
-      <c r="B35" s="15" t="inlineStr">
-        <is>
-          <t>사진이 없을 때 여기서 — 검색 금지</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n"/>
-      <c r="D35" s="14" t="n"/>
-      <c r="E35" s="14" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>GPT / 미리캔버스</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="14" t="n"/>
-      <c r="D36" s="14" t="n"/>
-      <c r="E36" s="14" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>※ 비밀번호는 여기 적지 않습니다. 담당자에게 따로 받으세요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="24" customHeight="1">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>5. 교육 일정과 제출물</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-    </row>
-    <row r="40" ht="24" customHeight="1">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>날짜</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>회차</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>내용</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>제출물</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>완료</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="22" customHeight="1">
-      <c r="A41" s="6" t="inlineStr">
-        <is>
-          <t>9/16 수</t>
-        </is>
-      </c>
-      <c r="B41" s="6" t="inlineStr">
-        <is>
-          <t>DAY 1</t>
-        </is>
-      </c>
-      <c r="C41" s="6" t="inlineStr">
-        <is>
-          <t>OT · 고정IP · 애니데스크 · 내 블로그 확인</t>
-        </is>
-      </c>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>계정 세팅 완료</t>
-        </is>
-      </c>
-      <c r="E41" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>9/17 목</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="inlineStr">
-        <is>
-          <t>DAY 2</t>
-        </is>
-      </c>
-      <c r="C42" s="6" t="inlineStr">
-        <is>
-          <t>네이버 이해 + 통검표 읽는 법</t>
-        </is>
-      </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>통검링크 10개 확인</t>
-        </is>
-      </c>
-      <c r="E42" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="22" customHeight="1">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>9/18 금</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="inlineStr">
-        <is>
-          <t>DAY 3</t>
-        </is>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>①통검표 + ②키워드 선정·제목 (★토요일 몫까지)</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>선정 + 제목 1개</t>
-        </is>
-      </c>
-      <c r="E43" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>9/19 토</t>
-        </is>
-      </c>
-      <c r="B44" s="6" t="inlineStr">
-        <is>
-          <t>DAY 4</t>
-        </is>
-      </c>
-      <c r="C44" s="6" t="inlineStr">
-        <is>
-          <t>③원고 쓰기만 — 어제 고른 키워드로 (4시간)</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>원고 1편</t>
-        </is>
-      </c>
-      <c r="E44" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="6" t="inlineStr">
-        <is>
-          <t>9/21 월</t>
-        </is>
-      </c>
-      <c r="B45" s="6" t="inlineStr">
-        <is>
-          <t>DAY 5</t>
-        </is>
-      </c>
-      <c r="C45" s="6" t="inlineStr">
-        <is>
-          <t>①②③반복 + ④사진·카드뉴스 · ★검색사진 금지</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>원고 + 카드뉴스</t>
-        </is>
-      </c>
-      <c r="E45" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="22" customHeight="1">
-      <c r="A46" s="6" t="inlineStr">
-        <is>
-          <t>9/22 화</t>
-        </is>
-      </c>
-      <c r="B46" s="6" t="inlineStr">
-        <is>
-          <t>DAY 6</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>⑤발행 배우기 + ★1편 처음부터 혼자</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>★ 2편 발행</t>
-        </is>
-      </c>
-      <c r="E46" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="22" customHeight="1">
-      <c r="A47" s="6" t="inlineStr">
-        <is>
-          <t>9/23 수</t>
-        </is>
-      </c>
-      <c r="B47" s="6" t="inlineStr">
-        <is>
-          <t>DAY 7</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>혼자 하루 2편 + 피드백</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>★ 2편 발행</t>
-        </is>
-      </c>
-      <c r="E47" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>9/24 목</t>
-        </is>
-      </c>
-      <c r="B48" s="6" t="inlineStr">
-        <is>
-          <t>DAY 8</t>
-        </is>
-      </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>혼자 하루 2편 + 총정리·인수인계</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>★ 2편 발행 (누적 6)</t>
-        </is>
-      </c>
-      <c r="E48" s="18" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="24" customHeight="1">
-      <c r="A50" s="11" t="inlineStr">
-        <is>
-          <t>6. 교육이 끝난 뒤</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-    </row>
-    <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>근무 시간</t>
-        </is>
-      </c>
-      <c r="B51" s="15" t="inlineStr">
-        <is>
-          <t>평일 08:00~17:00 (점심 12:00~13:00) / 토요일 08:00~12:00</t>
-        </is>
-      </c>
-      <c r="C51" s="14" t="n"/>
-      <c r="D51" s="14" t="n"/>
-      <c r="E51" s="14" t="n"/>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>하루 목표 편수</t>
-        </is>
-      </c>
-      <c r="B52" s="15" t="inlineStr">
-        <is>
-          <t>★ 초반 평일 2편 / 토요일 1편 → 익숙해지면 평일 2~4편 / 토요일 1~2편</t>
-        </is>
-      </c>
-      <c r="C52" s="14" t="n"/>
-      <c r="D52" s="14" t="n"/>
-      <c r="E52" s="14" t="n"/>
-    </row>
-    <row r="53" ht="34" customHeight="1">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>오늘 할 일 3가지</t>
-        </is>
-      </c>
-      <c r="B53" s="19" t="inlineStr">
-        <is>
-          <t>① 통검표 확인 및 수정  ② 어제 발행한 글 노출 체크  ③ 원고 제작 및 발행 — 매일 이 순서</t>
-        </is>
-      </c>
-      <c r="C53" s="20" t="n"/>
-      <c r="D53" s="20" t="n"/>
-      <c r="E53" s="20" t="n"/>
-    </row>
-    <row r="54" ht="34" customHeight="1">
-      <c r="A54" s="13" t="inlineStr">
-        <is>
-          <t>토요일에 할 일</t>
-        </is>
-      </c>
-      <c r="B54" s="15" t="inlineStr">
-        <is>
-          <t>다음 주 키워드 미리 선정 / 키워드 점검 / ★ 세이브 원고 만들어 두기 / 카드뉴스 / 노출 체크</t>
-        </is>
-      </c>
-      <c r="C54" s="14" t="n"/>
-      <c r="D54" s="14" t="n"/>
-      <c r="E54" s="14" t="n"/>
-    </row>
-    <row r="55" ht="44" customHeight="1">
-      <c r="A55" s="13" t="inlineStr">
-        <is>
-          <t>공휴일·연휴</t>
-        </is>
-      </c>
-      <c r="B55" s="15" t="inlineStr">
-        <is>
-          <t>쉬기 전에 담당자와 상의해 발행 갯수를 정하고 → 그만큼 원고를 미리 뽑아 → 블로그 예약 발행. 갯수를 무조건 맞출 필요는 없지만 최대한 할 수 있는 데까지</t>
-        </is>
-      </c>
-      <c r="C55" s="14" t="n"/>
-      <c r="D55" s="14" t="n"/>
-      <c r="E55" s="14" t="n"/>
-    </row>
-    <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>연차 신청</t>
-        </is>
-      </c>
-      <c r="B56" s="15" t="inlineStr">
-        <is>
-          <t>디자인팀 수수님에게 전달 (1주일 전, 사유와 함께)</t>
-        </is>
-      </c>
-      <c r="C56" s="14" t="n"/>
-      <c r="D56" s="14" t="n"/>
-      <c r="E56" s="14" t="n"/>
-    </row>
-    <row r="57" ht="22" customHeight="1">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>보고 요일 · 시간</t>
-        </is>
-      </c>
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="14" t="n"/>
-      <c r="D57" s="14" t="n"/>
-      <c r="E57" s="14" t="n"/>
-    </row>
-    <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>보고 채널</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>바이버 팀 그룹방 — 출퇴근 보고·연차 신청·발행 링크</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="n"/>
-      <c r="D58" s="14" t="n"/>
-      <c r="E58" s="14" t="n"/>
-    </row>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>질문 담당자 (1:1)</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="inlineStr">
-        <is>
-          <t>바이버 계정</t>
-        </is>
-      </c>
-      <c r="C59" s="14" t="n"/>
-      <c r="D59" s="14" t="n"/>
-      <c r="E59" s="14" t="n"/>
-    </row>
-    <row r="60" ht="44" customHeight="1">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>★ 발행 전 중간 보고</t>
-        </is>
-      </c>
-      <c r="B60" s="19" t="inlineStr">
-        <is>
-          <t>익숙해지기 전까지는 원고+사진+카드뉴스가 완성되면 담당자에게 먼저 보내 확인받고 발행합니다. 보낼 것 3가지 — 제목·키워드 / 원고 / 카드뉴스 이미지 전체</t>
-        </is>
-      </c>
-      <c r="C60" s="20" t="n"/>
-      <c r="D60" s="20" t="n"/>
-      <c r="E60" s="20" t="n"/>
-    </row>
-    <row r="61" ht="44" customHeight="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>막혔을 때</t>
-        </is>
-      </c>
-      <c r="B61" s="19" t="inlineStr">
-        <is>
-          <t>혼자 10분 넘게 막히면 바로 질문. ①뭘 하려고 했는지 ②어디서 막혔는지 ③화면 캡처 — 3가지를 같이 보냅니다</t>
-        </is>
-      </c>
-      <c r="C61" s="20" t="n"/>
-      <c r="D61" s="20" t="n"/>
-      <c r="E61" s="20" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="A39:E39"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B55:E55"/>
-    <mergeCell ref="B5:E5"/>
-    <mergeCell ref="B51:E51"/>
-    <mergeCell ref="B36:E36"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B35:E35"/>
-    <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="A37:E37"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="A50:E50"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B58:E58"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B61:E61"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="B57:E57"/>
-    <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B13:E13"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="A9:E9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
 </file>